--- a/Deliverables/BOM/Sensor-Board/eSpark_BOM-Sensor-Board.xlsx
+++ b/Deliverables/BOM/Sensor-Board/eSpark_BOM-Sensor-Board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Sensor-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B14C4E5-B0BF-499D-83A5-173AC3C63E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB58B122-5A91-43F9-B017-AD98AA54EA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22665" yWindow="1575" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21720" yWindow="3390" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="76">
   <si>
     <t>Component list</t>
   </si>
@@ -65,18 +65,9 @@
     <t>Designator</t>
   </si>
   <si>
-    <t>C1, C22, C46, C48, C50, C54, C56, C58, C60, C65, C66, C67, C68, C73, C74, C75, C76</t>
-  </si>
-  <si>
-    <t>C16, C45, C47, C49, C53, C55, C57, C59</t>
-  </si>
-  <si>
     <t>C51, C52</t>
   </si>
   <si>
-    <t>C61, C62, C63, C64, C69, C70, C71, C72</t>
-  </si>
-  <si>
     <t>J1</t>
   </si>
   <si>
@@ -86,21 +77,9 @@
     <t>P1, P2, P3, P4, P5, P6, P7, P8, P9, P10, P11, P12, P13, P14, P15, P16, P17, P18, P19</t>
   </si>
   <si>
-    <t>R17, R18, R19, R20, R21, R22, R23, R24</t>
-  </si>
-  <si>
     <t>R25, R26</t>
   </si>
   <si>
-    <t>R27, R28, R29, R30, R35, R36, R37, R38</t>
-  </si>
-  <si>
-    <t>R31, R32, R33, R34, R39, R40, R41, R42</t>
-  </si>
-  <si>
-    <t>U8, U9, U10, U11, U12, U13, U14, U15</t>
-  </si>
-  <si>
     <t>U16</t>
   </si>
   <si>
@@ -113,15 +92,9 @@
     <t>CAP CER 0.1UF 50V X7R 0402</t>
   </si>
   <si>
-    <t>CAP CER 10UF 25V X5R 0603</t>
-  </si>
-  <si>
     <t>CAP CER 1UF 16V X5R 0402</t>
   </si>
   <si>
-    <t>Cap Ceramic 0.022uF 25V X7R 10% Pad SMD 0402</t>
-  </si>
-  <si>
     <t>CONN FFC BOTTOM 24POS 0.50MM R/A</t>
   </si>
   <si>
@@ -131,21 +104,9 @@
     <t>Test Point ON</t>
   </si>
   <si>
-    <t>RES SMD 0402 240 Ohm 1% 1/16W ±100ppm/°C Molded SMD Paper T/R</t>
-  </si>
-  <si>
     <t>1/10W Thin Film Resistor 75V ±0.5% ±25ppm/℃ -55℃~+155℃ 64kΩ 0603 Chip Resistor - Surface Mount ROHS</t>
   </si>
   <si>
-    <t>Res Thick Film 0402 6.8K Ohm 5% 0.063W(1/16W) ±100ppm/C Pad SMD T/R</t>
-  </si>
-  <si>
-    <t>RES SMD 0402 150kOhm 5% Paper T/R</t>
-  </si>
-  <si>
-    <t>IC OPAMP INSTR 825KHZ 8SOIC</t>
-  </si>
-  <si>
     <t>SOT-23-5 Operational Amplifier ROHS</t>
   </si>
   <si>
@@ -158,24 +119,15 @@
     <t>Cap 0402</t>
   </si>
   <si>
-    <t>Cap0603</t>
-  </si>
-  <si>
     <t>FH12-24S-0.5SH(55)</t>
   </si>
   <si>
     <t>FH34SRJ-12S-0.5SH(50)</t>
   </si>
   <si>
-    <t>Res0402</t>
-  </si>
-  <si>
     <t>Res0603</t>
   </si>
   <si>
-    <t>SOIC-8</t>
-  </si>
-  <si>
     <t>SOT-23-5</t>
   </si>
   <si>
@@ -188,27 +140,9 @@
     <t>GRM155R71H104ME14D</t>
   </si>
   <si>
-    <t>CL10A106MA8NRNC</t>
-  </si>
-  <si>
     <t>CC0402KRX5R7BB105</t>
   </si>
   <si>
-    <t>CGA2B2X7R1E223K050BA</t>
-  </si>
-  <si>
-    <t>RC0402FR-07240RL</t>
-  </si>
-  <si>
-    <t>RC0402JR-076K8L</t>
-  </si>
-  <si>
-    <t>RC0402JR-07150KL</t>
-  </si>
-  <si>
-    <t>AD8221ARZ-R7</t>
-  </si>
-  <si>
     <t>TPMCP6021T-E/OT</t>
   </si>
   <si>
@@ -221,24 +155,15 @@
     <t>Murata</t>
   </si>
   <si>
-    <t>Samsung</t>
-  </si>
-  <si>
     <t>Yageo</t>
   </si>
   <si>
-    <t>TDK</t>
-  </si>
-  <si>
     <t>Hirose</t>
   </si>
   <si>
     <t>iking Tech</t>
   </si>
   <si>
-    <t>Analog Devices</t>
-  </si>
-  <si>
     <t>TECH PUBLIC</t>
   </si>
   <si>
@@ -251,27 +176,12 @@
     <t>0.1uF</t>
   </si>
   <si>
-    <t>10uF'</t>
-  </si>
-  <si>
     <t>1uF</t>
   </si>
   <si>
-    <t>22nF</t>
-  </si>
-  <si>
-    <t>240R</t>
-  </si>
-  <si>
     <t>64K</t>
   </si>
   <si>
-    <t>6K8</t>
-  </si>
-  <si>
-    <t>150K</t>
-  </si>
-  <si>
     <t>Custom</t>
   </si>
   <si>
@@ -320,33 +230,15 @@
     <t>C325464</t>
   </si>
   <si>
-    <t>---------</t>
-  </si>
-  <si>
     <t>--------</t>
   </si>
   <si>
-    <t>C2922482</t>
-  </si>
-  <si>
     <t>C424659</t>
   </si>
   <si>
-    <t>C114755</t>
-  </si>
-  <si>
     <t>C202112</t>
   </si>
   <si>
-    <t>C137847</t>
-  </si>
-  <si>
-    <t>C137919</t>
-  </si>
-  <si>
-    <t>C13342</t>
-  </si>
-  <si>
     <t>C2923365</t>
   </si>
   <si>
@@ -365,13 +257,7 @@
     <t>Single Board Cost</t>
   </si>
   <si>
-    <t xml:space="preserve">Need Low Price Link @urooj </t>
-  </si>
-  <si>
-    <t>CGA2B2X7R1E223KT0Y0F</t>
-  </si>
-  <si>
-    <t>C76703</t>
+    <t>C1, C60</t>
   </si>
 </sst>
 </file>
@@ -539,9 +425,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <sz val="9"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -942,7 +826,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1018,11 +902,180 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="3" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1030,23 +1083,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1056,189 +1097,26 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="3" borderId="30" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1577,7 +1455,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -1608,8 +1486,8 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="33"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="101"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1625,15 +1503,15 @@
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="55"/>
-      <c r="R2" s="56"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+      <c r="Q2" s="92"/>
+      <c r="R2" s="93"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -1657,7 +1535,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="34"/>
+      <c r="R3" s="90"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1681,7 +1559,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="35"/>
+      <c r="R4" s="91"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1705,7 +1583,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
-      <c r="R5" s="35"/>
+      <c r="R5" s="91"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1725,7 +1603,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="35"/>
+      <c r="R6" s="91"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1745,14 +1623,14 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="35"/>
+      <c r="R7" s="91"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="B8" s="44"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="46"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="38"/>
       <c r="F8" s="17"/>
       <c r="G8" s="17"/>
       <c r="H8" s="7"/>
@@ -1765,890 +1643,564 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="35"/>
+      <c r="R8" s="91"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="H9" s="39" t="s">
+      <c r="D9" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="K9" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="L9" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="N9" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="O9" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="P9" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q9" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="R9" s="47" t="s">
         <v>61</v>
-      </c>
-      <c r="I9" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="J9" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="K9" s="59" t="s">
-        <v>84</v>
-      </c>
-      <c r="L9" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="M9" s="57" t="s">
-        <v>86</v>
-      </c>
-      <c r="N9" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="O9" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="P9" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q9" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="R9" s="59" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="86">
+      <c r="B10" s="73">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="90" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="47" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="94" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" s="47" t="s">
-        <v>92</v>
-      </c>
-      <c r="H10" s="90" t="s">
+      <c r="C10" s="102" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="77" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="81" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="J10" s="90" t="s">
-        <v>72</v>
-      </c>
-      <c r="K10" s="60">
-        <v>17</v>
-      </c>
-      <c r="L10" s="48">
+      <c r="H10" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="J10" s="77" t="s">
+        <v>47</v>
+      </c>
+      <c r="K10" s="48">
+        <v>2</v>
+      </c>
+      <c r="L10" s="40">
         <f>K10*5</f>
-        <v>85</v>
-      </c>
-      <c r="M10" s="72">
-        <v>100</v>
-      </c>
-      <c r="N10" s="81" t="s">
-        <v>94</v>
-      </c>
-      <c r="O10" s="76">
-        <v>6.7000000000000002E-3</v>
-      </c>
-      <c r="P10" s="70">
+        <v>10</v>
+      </c>
+      <c r="M10" s="60">
+        <v>50</v>
+      </c>
+      <c r="N10" s="69" t="s">
+        <v>64</v>
+      </c>
+      <c r="O10" s="64">
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="P10" s="58">
         <f>O10*M10</f>
-        <v>0.67</v>
-      </c>
-      <c r="Q10" s="65"/>
-      <c r="R10" s="60"/>
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="Q10" s="53"/>
+      <c r="R10" s="48"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="87">
-        <f t="shared" ref="B11:B23" si="0">ROW(B11) - ROW($B$9)</f>
+      <c r="B11" s="74">
+        <f>ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="91" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" s="96" t="s">
-        <v>96</v>
-      </c>
-      <c r="H11" s="91" t="s">
-        <v>63</v>
-      </c>
-      <c r="I11" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="J11" s="91" t="s">
-        <v>73</v>
-      </c>
-      <c r="K11" s="61">
-        <v>8</v>
+      <c r="C11" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="78" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="82" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="78" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11" s="78" t="s">
+        <v>48</v>
+      </c>
+      <c r="K11" s="49">
+        <v>2</v>
       </c>
       <c r="L11" s="31">
-        <f t="shared" ref="L11:L23" si="1">K11*5</f>
-        <v>40</v>
-      </c>
-      <c r="M11" s="73">
-        <v>60</v>
-      </c>
-      <c r="N11" s="82" t="s">
-        <v>94</v>
-      </c>
-      <c r="O11" s="77">
-        <v>1.3599999999999999E-2</v>
-      </c>
-      <c r="P11" s="84">
-        <f t="shared" ref="P11:P23" si="2">O11*M11</f>
-        <v>0.81599999999999995</v>
-      </c>
-      <c r="Q11" s="66"/>
-      <c r="R11" s="61"/>
+        <f t="shared" ref="L11:L17" si="0">K11*5</f>
+        <v>10</v>
+      </c>
+      <c r="M11" s="61">
+        <v>50</v>
+      </c>
+      <c r="N11" s="70" t="s">
+        <v>64</v>
+      </c>
+      <c r="O11" s="65">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="P11" s="71">
+        <f t="shared" ref="P11:P17" si="1">O11*M11</f>
+        <v>0.32</v>
+      </c>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="49"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="87">
+      <c r="B12" s="74">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="79" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="79" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="67" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="79" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J12" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="K12" s="50">
+        <v>1</v>
+      </c>
+      <c r="L12" s="30">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="M12" s="62">
+        <v>6</v>
+      </c>
+      <c r="N12" s="88" t="s">
+        <v>64</v>
+      </c>
+      <c r="O12" s="66">
+        <v>0.56089999999999995</v>
+      </c>
+      <c r="P12" s="59">
+        <f t="shared" si="1"/>
+        <v>3.3653999999999997</v>
+      </c>
+      <c r="Q12" s="55"/>
+      <c r="R12" s="50"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="74">
+        <f t="shared" ref="B13:B17" si="2">ROW(B13) - ROW($B$9)</f>
+        <v>4</v>
+      </c>
+      <c r="C13" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="92" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="92" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="H12" s="92" t="s">
+      <c r="D13" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="78" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="82" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="78" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="J13" s="84" t="s">
+        <v>51</v>
+      </c>
+      <c r="K13" s="49">
+        <v>1</v>
+      </c>
+      <c r="L13" s="31">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="M13" s="61">
+        <v>6</v>
+      </c>
+      <c r="N13" s="70" t="s">
         <v>64</v>
       </c>
-      <c r="I12" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="J12" s="92" t="s">
-        <v>74</v>
-      </c>
-      <c r="K12" s="62">
-        <v>2</v>
-      </c>
-      <c r="L12" s="30">
+      <c r="O13" s="65">
+        <v>0.1893</v>
+      </c>
+      <c r="P13" s="71">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="M12" s="74">
-        <v>50</v>
-      </c>
-      <c r="N12" s="83" t="s">
-        <v>94</v>
-      </c>
-      <c r="O12" s="78">
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="P12" s="71">
-        <f t="shared" si="2"/>
-        <v>0.32</v>
-      </c>
-      <c r="Q12" s="67"/>
-      <c r="R12" s="62"/>
-    </row>
-    <row r="13" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="87">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C13" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="91" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" s="95" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="H13" s="91" t="s">
-        <v>65</v>
-      </c>
-      <c r="I13" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="J13" s="91" t="s">
-        <v>75</v>
-      </c>
-      <c r="K13" s="61">
-        <v>8</v>
-      </c>
-      <c r="L13" s="31">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="M13" s="73">
-        <v>50</v>
-      </c>
-      <c r="N13" s="82" t="s">
-        <v>94</v>
-      </c>
-      <c r="O13" s="77">
-        <v>8.0999999999999996E-3</v>
-      </c>
-      <c r="P13" s="84">
-        <f t="shared" si="2"/>
-        <v>0.40499999999999997</v>
-      </c>
-      <c r="Q13" s="66"/>
-      <c r="R13" s="61"/>
+        <v>1.1357999999999999</v>
+      </c>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="49"/>
     </row>
     <row r="14" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="87">
+      <c r="B14" s="74">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="79" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="67" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="I14" s="67" t="s">
+        <v>66</v>
+      </c>
+      <c r="J14" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="K14" s="50">
+        <v>19</v>
+      </c>
+      <c r="L14" s="30">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
+      <c r="M14" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="O14" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="P14" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q14" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="R14" s="51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="74">
+        <f>ROW(B15) - ROW($B$9)</f>
+        <v>6</v>
+      </c>
+      <c r="C15" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="92" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="F14" s="92" t="s">
+      <c r="D15" s="78" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="78" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" s="82" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="H14" s="92" t="s">
-        <v>66</v>
-      </c>
-      <c r="I14" s="41" t="s">
-        <v>101</v>
-      </c>
-      <c r="J14" s="68" t="s">
-        <v>81</v>
-      </c>
-      <c r="K14" s="62">
-        <v>1</v>
-      </c>
-      <c r="L14" s="30">
+      <c r="I15" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="J15" s="78" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="49">
+        <v>2</v>
+      </c>
+      <c r="L15" s="31">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M15" s="61">
+        <v>50</v>
+      </c>
+      <c r="N15" s="70" t="s">
+        <v>64</v>
+      </c>
+      <c r="O15" s="65">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="P15" s="71">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="M14" s="74">
-        <v>6</v>
-      </c>
-      <c r="N14" s="103" t="s">
-        <v>94</v>
-      </c>
-      <c r="O14" s="78">
-        <v>0.56089999999999995</v>
-      </c>
-      <c r="P14" s="71">
-        <f t="shared" si="2"/>
-        <v>3.3653999999999997</v>
-      </c>
-      <c r="Q14" s="67"/>
-      <c r="R14" s="62"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="87">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="91" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="F15" s="91" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="96" t="s">
-        <v>97</v>
-      </c>
-      <c r="H15" s="91" t="s">
-        <v>66</v>
-      </c>
-      <c r="I15" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="J15" s="98" t="s">
-        <v>81</v>
-      </c>
-      <c r="K15" s="61">
-        <v>1</v>
-      </c>
-      <c r="L15" s="31">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="M15" s="73">
-        <v>6</v>
-      </c>
-      <c r="N15" s="82" t="s">
-        <v>94</v>
-      </c>
-      <c r="O15" s="77">
-        <v>0.1893</v>
-      </c>
-      <c r="P15" s="84">
-        <f t="shared" si="2"/>
-        <v>1.1357999999999999</v>
-      </c>
-      <c r="Q15" s="66"/>
-      <c r="R15" s="61"/>
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="Q15" s="54"/>
+      <c r="R15" s="49"/>
     </row>
     <row r="16" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="87">
+      <c r="B16" s="74">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="79" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="79" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="67" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="79" t="s">
+        <v>44</v>
+      </c>
+      <c r="I16" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="J16" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="K16" s="50">
+        <v>1</v>
+      </c>
+      <c r="L16" s="30">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="M16" s="62">
+        <v>6</v>
+      </c>
+      <c r="N16" s="88" t="s">
+        <v>64</v>
+      </c>
+      <c r="O16" s="66">
+        <v>0.44180000000000003</v>
+      </c>
+      <c r="P16" s="59">
+        <f t="shared" si="1"/>
+        <v>2.6508000000000003</v>
+      </c>
+      <c r="Q16" s="55"/>
+      <c r="R16" s="50"/>
+    </row>
+    <row r="17" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="B17" s="75">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="F16" s="68" t="s">
-        <v>81</v>
-      </c>
-      <c r="G16" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="H16" s="68" t="s">
-        <v>81</v>
-      </c>
-      <c r="I16" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="J16" s="68" t="s">
-        <v>81</v>
-      </c>
-      <c r="K16" s="62">
-        <v>19</v>
-      </c>
-      <c r="L16" s="30">
-        <f t="shared" si="1"/>
-        <v>95</v>
-      </c>
-      <c r="M16" s="58" t="s">
-        <v>81</v>
-      </c>
-      <c r="N16" s="68" t="s">
-        <v>97</v>
-      </c>
-      <c r="O16" s="79" t="s">
-        <v>81</v>
-      </c>
-      <c r="P16" s="68" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q16" s="68" t="s">
-        <v>97</v>
-      </c>
-      <c r="R16" s="63" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="87">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C17" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="91" t="s">
+      <c r="D17" s="80" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="40" t="s">
+      <c r="F17" s="80" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="83" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="91" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" s="96" t="s">
-        <v>97</v>
-      </c>
-      <c r="H17" s="91" t="s">
-        <v>64</v>
-      </c>
-      <c r="I17" s="40" t="s">
-        <v>100</v>
-      </c>
-      <c r="J17" s="91" t="s">
-        <v>76</v>
-      </c>
-      <c r="K17" s="61">
-        <v>8</v>
-      </c>
-      <c r="L17" s="31">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="M17" s="73">
-        <v>100</v>
-      </c>
-      <c r="N17" s="82" t="s">
-        <v>94</v>
-      </c>
-      <c r="O17" s="77">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="P17" s="84">
-        <f t="shared" si="2"/>
-        <v>0.08</v>
-      </c>
-      <c r="Q17" s="66"/>
-      <c r="R17" s="61"/>
-    </row>
-    <row r="18" spans="1:18" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="87">
-        <f>ROW(B18) - ROW($B$9)</f>
-        <v>9</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="92" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="92" t="s">
-        <v>107</v>
-      </c>
-      <c r="G18" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="H18" s="92" t="s">
-        <v>67</v>
-      </c>
-      <c r="I18" s="41" t="s">
-        <v>108</v>
-      </c>
-      <c r="J18" s="92" t="s">
-        <v>77</v>
-      </c>
-      <c r="K18" s="62">
+      <c r="I17" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="J17" s="85" t="s">
+        <v>51</v>
+      </c>
+      <c r="K17" s="52">
         <v>2</v>
       </c>
-      <c r="L18" s="30">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="M18" s="74">
-        <v>50</v>
-      </c>
-      <c r="N18" s="103" t="s">
-        <v>94</v>
-      </c>
-      <c r="O18" s="78">
-        <v>1.2699999999999999E-2</v>
-      </c>
-      <c r="P18" s="71">
-        <f t="shared" si="2"/>
-        <v>0.63500000000000001</v>
-      </c>
-      <c r="Q18" s="67"/>
-      <c r="R18" s="62"/>
-    </row>
-    <row r="19" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="87">
+      <c r="L17" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="91" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="40" t="s">
-        <v>45</v>
-      </c>
-      <c r="F19" s="91" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19" s="96" t="s">
-        <v>97</v>
-      </c>
-      <c r="H19" s="91" t="s">
+      <c r="M17" s="63">
+        <v>6</v>
+      </c>
+      <c r="N17" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="I19" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="J19" s="91" t="s">
-        <v>78</v>
-      </c>
-      <c r="K19" s="61">
-        <v>8</v>
-      </c>
-      <c r="L19" s="31">
+      <c r="O17" s="68">
+        <v>0.15240000000000001</v>
+      </c>
+      <c r="P17" s="72">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="M19" s="73">
-        <v>100</v>
-      </c>
-      <c r="N19" s="82" t="s">
-        <v>94</v>
-      </c>
-      <c r="O19" s="77">
-        <v>2.7000000000000001E-3</v>
-      </c>
-      <c r="P19" s="84">
-        <f t="shared" si="2"/>
-        <v>0.27</v>
-      </c>
-      <c r="Q19" s="66"/>
-      <c r="R19" s="61"/>
+        <v>0.9144000000000001</v>
+      </c>
+      <c r="Q17" s="57"/>
+      <c r="R17" s="52"/>
     </row>
-    <row r="20" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="87">
-        <f>ROW(B20) - ROW($B$9)</f>
-        <v>11</v>
-      </c>
-      <c r="C20" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="92" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="92" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="H20" s="92" t="s">
-        <v>64</v>
-      </c>
-      <c r="I20" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="J20" s="92" t="s">
-        <v>79</v>
-      </c>
-      <c r="K20" s="62">
-        <v>8</v>
-      </c>
-      <c r="L20" s="30">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="M20" s="74">
-        <v>100</v>
-      </c>
-      <c r="N20" s="103" t="s">
-        <v>94</v>
-      </c>
-      <c r="O20" s="78">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="P20" s="71">
-        <f t="shared" si="2"/>
-        <v>0.05</v>
-      </c>
-      <c r="Q20" s="67"/>
-      <c r="R20" s="62"/>
+    <row r="18" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="44"/>
+      <c r="E18" s="96"/>
+      <c r="F18" s="96"/>
+      <c r="G18" s="96"/>
+      <c r="H18" s="96"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="96"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="97"/>
+      <c r="M18" s="94" t="s">
+        <v>73</v>
+      </c>
+      <c r="N18" s="95"/>
+      <c r="O18" s="95"/>
+      <c r="P18" s="86">
+        <f>SUM(P10:P17)</f>
+        <v>9.3864000000000001</v>
+      </c>
+      <c r="Q18" s="96"/>
+      <c r="R18" s="97"/>
     </row>
-    <row r="21" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="87">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="C21" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="91" t="s">
-        <v>37</v>
-      </c>
-      <c r="E21" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" s="91" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21" s="96" t="s">
-        <v>97</v>
-      </c>
-      <c r="H21" s="91" t="s">
-        <v>68</v>
-      </c>
-      <c r="I21" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="J21" s="98" t="s">
-        <v>81</v>
-      </c>
-      <c r="K21" s="61">
-        <v>8</v>
-      </c>
-      <c r="L21" s="31">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="M21" s="73">
-        <v>42</v>
-      </c>
-      <c r="N21" s="82" t="s">
-        <v>94</v>
-      </c>
-      <c r="O21" s="77">
-        <v>5.9004000000000003</v>
-      </c>
-      <c r="P21" s="84">
-        <f t="shared" si="2"/>
-        <v>247.8168</v>
-      </c>
-      <c r="Q21" s="100" t="s">
-        <v>111</v>
-      </c>
-      <c r="R21" s="61"/>
-    </row>
-    <row r="22" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="87">
-        <f>ROW(B22) - ROW($B$9)</f>
-        <v>13</v>
-      </c>
-      <c r="C22" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="92" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="92" t="s">
-        <v>59</v>
-      </c>
-      <c r="G22" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="H22" s="92" t="s">
-        <v>69</v>
-      </c>
-      <c r="I22" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="J22" s="68" t="s">
-        <v>81</v>
-      </c>
-      <c r="K22" s="62">
-        <v>1</v>
-      </c>
-      <c r="L22" s="30">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="M22" s="74">
+    <row r="19" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="N22" s="103" t="s">
-        <v>94</v>
-      </c>
-      <c r="O22" s="78">
-        <v>0.44180000000000003</v>
-      </c>
-      <c r="P22" s="71">
-        <f t="shared" si="2"/>
-        <v>2.6508000000000003</v>
-      </c>
-      <c r="Q22" s="67"/>
-      <c r="R22" s="62"/>
-    </row>
-    <row r="23" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="88">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="C23" s="89" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="93" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" s="89" t="s">
-        <v>49</v>
-      </c>
-      <c r="F23" s="93" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23" s="97" t="s">
-        <v>97</v>
-      </c>
-      <c r="H23" s="93" t="s">
-        <v>70</v>
-      </c>
-      <c r="I23" s="89" t="s">
-        <v>106</v>
-      </c>
-      <c r="J23" s="99" t="s">
-        <v>81</v>
-      </c>
-      <c r="K23" s="64">
-        <v>2</v>
-      </c>
-      <c r="L23" s="49">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="M23" s="75">
-        <v>6</v>
-      </c>
-      <c r="N23" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="O23" s="80">
-        <v>0.15240000000000001</v>
-      </c>
-      <c r="P23" s="85">
-        <f t="shared" si="2"/>
-        <v>0.9144000000000001</v>
-      </c>
-      <c r="Q23" s="69"/>
-      <c r="R23" s="64"/>
-    </row>
-    <row r="24" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="52"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="54"/>
-      <c r="M24" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="N24" s="43"/>
-      <c r="O24" s="43"/>
-      <c r="P24" s="101">
-        <f>SUM(P10:P23)</f>
-        <v>259.12919999999997</v>
-      </c>
-      <c r="Q24" s="53"/>
-      <c r="R24" s="54"/>
-    </row>
-    <row r="25" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="37"/>
-      <c r="M25" s="42" t="s">
-        <v>110</v>
-      </c>
-      <c r="N25" s="43"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="102">
-        <f>P24/5</f>
-        <v>51.825839999999992</v>
-      </c>
-      <c r="Q25" s="36"/>
-      <c r="R25" s="37"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="98"/>
+      <c r="F19" s="98"/>
+      <c r="G19" s="98"/>
+      <c r="H19" s="98"/>
+      <c r="I19" s="98"/>
+      <c r="J19" s="98"/>
+      <c r="K19" s="98"/>
+      <c r="L19" s="99"/>
+      <c r="M19" s="94" t="s">
+        <v>74</v>
+      </c>
+      <c r="N19" s="95"/>
+      <c r="O19" s="95"/>
+      <c r="P19" s="87">
+        <f>P18/5</f>
+        <v>1.8772800000000001</v>
+      </c>
+      <c r="Q19" s="98"/>
+      <c r="R19" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="J1:K1"/>
     <mergeCell ref="R3:R8"/>
     <mergeCell ref="J2:R2"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="E24:L25"/>
-    <mergeCell ref="Q24:R25"/>
-    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="E18:L19"/>
+    <mergeCell ref="Q18:R19"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="N10" r:id="rId1" xr:uid="{100462C4-FA8F-4D16-8168-575F3EAD1350}"/>
-    <hyperlink ref="N12" r:id="rId2" xr:uid="{CC1A75C7-134E-4E20-A6A5-5C056D4918B2}"/>
-    <hyperlink ref="N11" r:id="rId3" xr:uid="{B7714D11-A77B-454C-8828-A5BD4A746644}"/>
-    <hyperlink ref="N15" r:id="rId4" xr:uid="{FFF28CE1-87AC-4ADE-A95E-16C393CFA042}"/>
-    <hyperlink ref="N17" r:id="rId5" xr:uid="{A4714B3E-0454-4CEF-8B45-316738A110A7}"/>
-    <hyperlink ref="N14" r:id="rId6" xr:uid="{8C9B39EB-942A-43DB-BCEF-D599850185D7}"/>
-    <hyperlink ref="N19" r:id="rId7" xr:uid="{BE1297EE-8B2E-441B-955F-3A349B84EDE1}"/>
-    <hyperlink ref="N20" r:id="rId8" xr:uid="{0C3EC796-D75C-4C31-88F7-C2EE4D012568}"/>
-    <hyperlink ref="N21" r:id="rId9" xr:uid="{5A0D6039-D02A-49E6-B18A-455287F1C8C3}"/>
-    <hyperlink ref="N22" r:id="rId10" xr:uid="{BB22E13A-9E79-4097-AC4F-F19B2F2754A8}"/>
-    <hyperlink ref="N23" r:id="rId11" xr:uid="{DF4029E5-E8D3-4584-B881-A0621DBEE882}"/>
-    <hyperlink ref="N18" r:id="rId12" xr:uid="{28F214EC-7847-4913-BF43-3F44A00C2675}"/>
-    <hyperlink ref="N13" r:id="rId13" xr:uid="{38C6ACF0-DAFE-45AC-B84A-4C54E5BC2212}"/>
+    <hyperlink ref="N11" r:id="rId2" xr:uid="{CC1A75C7-134E-4E20-A6A5-5C056D4918B2}"/>
+    <hyperlink ref="N13" r:id="rId3" xr:uid="{FFF28CE1-87AC-4ADE-A95E-16C393CFA042}"/>
+    <hyperlink ref="N12" r:id="rId4" xr:uid="{8C9B39EB-942A-43DB-BCEF-D599850185D7}"/>
+    <hyperlink ref="N16" r:id="rId5" xr:uid="{BB22E13A-9E79-4097-AC4F-F19B2F2754A8}"/>
+    <hyperlink ref="N17" r:id="rId6" xr:uid="{DF4029E5-E8D3-4584-B881-A0621DBEE882}"/>
+    <hyperlink ref="N15" r:id="rId7" xr:uid="{28F214EC-7847-4913-BF43-3F44A00C2675}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
-  <drawing r:id="rId15"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
+  <drawing r:id="rId9"/>
 </worksheet>
 </file>
--- a/Deliverables/BOM/Sensor-Board/eSpark_BOM-Sensor-Board.xlsx
+++ b/Deliverables/BOM/Sensor-Board/eSpark_BOM-Sensor-Board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Sensor-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB58B122-5A91-43F9-B017-AD98AA54EA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF1ACAD-A226-4ACD-BB50-432073717BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21720" yWindow="3390" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="89">
   <si>
     <t>Component list</t>
   </si>
@@ -74,9 +74,6 @@
     <t>J2</t>
   </si>
   <si>
-    <t>P1, P2, P3, P4, P5, P6, P7, P8, P9, P10, P11, P12, P13, P14, P15, P16, P17, P18, P19</t>
-  </si>
-  <si>
     <t>R25, R26</t>
   </si>
   <si>
@@ -95,9 +92,6 @@
     <t>CAP CER 1UF 16V X5R 0402</t>
   </si>
   <si>
-    <t>CONN FFC BOTTOM 24POS 0.50MM R/A</t>
-  </si>
-  <si>
     <t>CONN FPC/FFC 12POS .5MM</t>
   </si>
   <si>
@@ -119,9 +113,6 @@
     <t>Cap 0402</t>
   </si>
   <si>
-    <t>FH12-24S-0.5SH(55)</t>
-  </si>
-  <si>
     <t>FH34SRJ-12S-0.5SH(50)</t>
   </si>
   <si>
@@ -236,9 +227,6 @@
     <t>C424659</t>
   </si>
   <si>
-    <t>C202112</t>
-  </si>
-  <si>
     <t>C2923365</t>
   </si>
   <si>
@@ -258,6 +246,57 @@
   </si>
   <si>
     <t>C1, C60</t>
+  </si>
+  <si>
+    <t>Slide Lock 32 Bottom Contact Surface Mount 0.5mm SMD,P=0.5mm FFC/FPC Connectors ROHS</t>
+  </si>
+  <si>
+    <t>AFC07-S32FCA-00</t>
+  </si>
+  <si>
+    <t>JUSHUO</t>
+  </si>
+  <si>
+    <t>P1, P3, P5, P7, P9, P11, P13, P15, P16, P18, P20</t>
+  </si>
+  <si>
+    <t>DO NOT MOUNT</t>
+  </si>
+  <si>
+    <t>R1, R2</t>
+  </si>
+  <si>
+    <t>RES SMD 10K OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>Res0402</t>
+  </si>
+  <si>
+    <t>RC0402FR-0710KL</t>
+  </si>
+  <si>
+    <t>10K</t>
+  </si>
+  <si>
+    <t>SW1, SW2</t>
+  </si>
+  <si>
+    <t>No Gull Wing 50mA 100MΩ 80000 260gf@±50gf 12V -25℃~+85℃ 1.7mm Golden Round Button Brick nogging SPST SMD Tactile Switches ROHS</t>
+  </si>
+  <si>
+    <t>TC-0522C-1.7-260G</t>
+  </si>
+  <si>
+    <t>HCTL</t>
+  </si>
+  <si>
+    <t>C262570</t>
+  </si>
+  <si>
+    <t>C60490</t>
+  </si>
+  <si>
+    <t>C2845290</t>
   </si>
 </sst>
 </file>
@@ -269,7 +308,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -281,6 +320,7 @@
       <sz val="10"/>
       <color indexed="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -430,6 +470,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -463,7 +519,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -819,6 +875,60 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -826,7 +936,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -945,9 +1055,6 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -999,21 +1106,6 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1029,12 +1121,6 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1050,15 +1136,9 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1071,11 +1151,116 @@
     <xf numFmtId="166" fontId="14" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="29" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="29" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1108,15 +1293,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1455,7 +1631,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -1486,8 +1662,8 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="101"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="114"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1503,15 +1679,15 @@
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
-      <c r="Q2" s="92"/>
-      <c r="R2" s="93"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="117"/>
+      <c r="O2" s="117"/>
+      <c r="P2" s="117"/>
+      <c r="Q2" s="117"/>
+      <c r="R2" s="118"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -1535,7 +1711,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="90"/>
+      <c r="R3" s="115"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1559,7 +1735,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
-      <c r="R4" s="91"/>
+      <c r="R4" s="116"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1583,7 +1759,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
-      <c r="R5" s="91"/>
+      <c r="R5" s="116"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1603,7 +1779,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="91"/>
+      <c r="R6" s="116"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1623,7 +1799,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="91"/>
+      <c r="R7" s="116"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1643,7 +1819,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="91"/>
+      <c r="R8" s="116"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1654,553 +1830,659 @@
         <v>10</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G9" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="L9" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="I9" s="32" t="s">
+      <c r="M9" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="J9" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="K9" s="47" t="s">
+      <c r="N9" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="L9" s="33" t="s">
+      <c r="O9" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="M9" s="45" t="s">
+      <c r="P9" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="N9" s="33" t="s">
+      <c r="Q9" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="O9" s="32" t="s">
+      <c r="R9" s="46" t="s">
         <v>58</v>
-      </c>
-      <c r="P9" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q9" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="R9" s="47" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="73">
+      <c r="B10" s="67">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="102" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" s="77" t="s">
-        <v>19</v>
+      <c r="C10" s="79" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="69" t="s">
+        <v>18</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F10" s="81" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="39" t="s">
-        <v>62</v>
-      </c>
-      <c r="H10" s="77" t="s">
-        <v>40</v>
+        <v>32</v>
+      </c>
+      <c r="G10" s="85" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="69" t="s">
+        <v>37</v>
       </c>
       <c r="I10" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="J10" s="77" t="s">
-        <v>47</v>
-      </c>
-      <c r="K10" s="48">
+        <v>60</v>
+      </c>
+      <c r="J10" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" s="47">
         <v>2</v>
       </c>
       <c r="L10" s="40">
         <f>K10*5</f>
         <v>10</v>
       </c>
-      <c r="M10" s="60">
+      <c r="M10" s="59">
         <v>50</v>
       </c>
-      <c r="N10" s="69" t="s">
-        <v>64</v>
-      </c>
-      <c r="O10" s="64">
-        <v>7.3000000000000001E-3</v>
-      </c>
-      <c r="P10" s="58">
+      <c r="N10" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="O10" s="57">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="P10" s="98">
         <f>O10*M10</f>
-        <v>0.36499999999999999</v>
-      </c>
-      <c r="Q10" s="53"/>
-      <c r="R10" s="48"/>
+        <v>0.36</v>
+      </c>
+      <c r="Q10" s="52"/>
+      <c r="R10" s="47"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="74">
-        <f>ROW(B11) - ROW($B$9)</f>
+      <c r="B11" s="67">
+        <f t="shared" ref="B11:B19" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="78" t="s">
-        <v>20</v>
+      <c r="D11" s="70" t="s">
+        <v>19</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="78" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="82" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" s="78" t="s">
-        <v>41</v>
+        <v>26</v>
+      </c>
+      <c r="F11" s="82" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="74" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="70" t="s">
+        <v>38</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="J11" s="78" t="s">
-        <v>48</v>
-      </c>
-      <c r="K11" s="49">
+        <v>62</v>
+      </c>
+      <c r="J11" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11" s="48">
         <v>2</v>
       </c>
       <c r="L11" s="31">
-        <f t="shared" ref="L11:L17" si="0">K11*5</f>
+        <f t="shared" ref="L11:L19" si="1">K11*5</f>
         <v>10</v>
       </c>
-      <c r="M11" s="61">
+      <c r="M11" s="60">
         <v>50</v>
       </c>
-      <c r="N11" s="70" t="s">
-        <v>64</v>
+      <c r="N11" s="64" t="s">
+        <v>61</v>
       </c>
       <c r="O11" s="65">
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="P11" s="71">
-        <f t="shared" ref="P11:P17" si="1">O11*M11</f>
-        <v>0.32</v>
-      </c>
-      <c r="Q11" s="54"/>
-      <c r="R11" s="49"/>
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="P11" s="99">
+        <f t="shared" ref="P11:P19" si="2">O11*M11</f>
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="Q11" s="53"/>
+      <c r="R11" s="48"/>
     </row>
-    <row r="12" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="48" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="74">
-        <f>ROW(B12) - ROW($B$9)</f>
+      <c r="B12" s="67">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C12" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="79" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="79" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="67" t="s">
-        <v>66</v>
-      </c>
-      <c r="H12" s="79" t="s">
-        <v>42</v>
+        <v>72</v>
+      </c>
+      <c r="E12" s="79" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="80" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="H12" s="69" t="s">
+        <v>74</v>
       </c>
       <c r="I12" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="J12" s="56" t="s">
-        <v>51</v>
-      </c>
-      <c r="K12" s="50">
+        <v>86</v>
+      </c>
+      <c r="J12" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="K12" s="49">
         <v>1</v>
       </c>
       <c r="L12" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M12" s="62">
+      <c r="M12" s="61">
         <v>6</v>
       </c>
-      <c r="N12" s="88" t="s">
-        <v>64</v>
-      </c>
-      <c r="O12" s="66">
-        <v>0.56089999999999995</v>
-      </c>
-      <c r="P12" s="59">
-        <f t="shared" si="1"/>
-        <v>3.3653999999999997</v>
-      </c>
-      <c r="Q12" s="55"/>
-      <c r="R12" s="50"/>
+      <c r="N12" s="96" t="s">
+        <v>61</v>
+      </c>
+      <c r="O12" s="58">
+        <v>0.1598</v>
+      </c>
+      <c r="P12" s="100">
+        <f t="shared" si="2"/>
+        <v>0.95879999999999999</v>
+      </c>
+      <c r="Q12" s="54"/>
+      <c r="R12" s="49"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="74">
-        <f t="shared" ref="B13:B17" si="2">ROW(B13) - ROW($B$9)</f>
+      <c r="B13" s="67">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="78" t="s">
-        <v>22</v>
+      <c r="D13" s="70" t="s">
+        <v>20</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="78" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="82" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" s="78" t="s">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="F13" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="74" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" s="70" t="s">
+        <v>39</v>
       </c>
       <c r="I13" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="J13" s="84" t="s">
-        <v>51</v>
-      </c>
-      <c r="K13" s="49">
+        <v>64</v>
+      </c>
+      <c r="J13" s="74" t="s">
+        <v>48</v>
+      </c>
+      <c r="K13" s="48">
         <v>1</v>
       </c>
       <c r="L13" s="31">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="M13" s="60">
+        <v>6</v>
+      </c>
+      <c r="N13" s="64" t="s">
+        <v>61</v>
+      </c>
+      <c r="O13" s="65">
+        <v>0.1893</v>
+      </c>
+      <c r="P13" s="99">
+        <f t="shared" si="2"/>
+        <v>1.1357999999999999</v>
+      </c>
+      <c r="Q13" s="53"/>
+      <c r="R13" s="48"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="67">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="M13" s="61">
+      <c r="C14" s="104" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="105" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="106" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="107" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="108" t="s">
+        <v>63</v>
+      </c>
+      <c r="H14" s="108" t="s">
+        <v>48</v>
+      </c>
+      <c r="I14" s="109" t="s">
+        <v>63</v>
+      </c>
+      <c r="J14" s="108" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" s="110">
+        <v>11</v>
+      </c>
+      <c r="L14" s="111">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="M14" s="112" t="s">
+        <v>48</v>
+      </c>
+      <c r="N14" s="108" t="s">
+        <v>63</v>
+      </c>
+      <c r="O14" s="108" t="s">
+        <v>48</v>
+      </c>
+      <c r="P14" s="109" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q14" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="R14" s="50"/>
+    </row>
+    <row r="15" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="67">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="N13" s="70" t="s">
-        <v>64</v>
-      </c>
-      <c r="O13" s="65">
-        <v>0.1893</v>
-      </c>
-      <c r="P13" s="71">
+      <c r="C15" s="70" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="70" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="74" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" s="70" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" s="73" t="s">
+        <v>87</v>
+      </c>
+      <c r="J15" s="70" t="s">
+        <v>81</v>
+      </c>
+      <c r="K15" s="53">
+        <v>2</v>
+      </c>
+      <c r="L15" s="31">
         <f t="shared" si="1"/>
-        <v>1.1357999999999999</v>
-      </c>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="49"/>
+        <v>10</v>
+      </c>
+      <c r="M15" s="93">
+        <v>100</v>
+      </c>
+      <c r="N15" s="97" t="s">
+        <v>61</v>
+      </c>
+      <c r="O15" s="74">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="P15" s="99">
+        <f t="shared" si="2"/>
+        <v>0.06</v>
+      </c>
+      <c r="Q15" s="94"/>
+      <c r="R15" s="95"/>
     </row>
-    <row r="14" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="74">
-        <f>ROW(B14) - ROW($B$9)</f>
+    <row r="16" spans="1:18" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="67">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="83" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" s="71" t="s">
+        <v>40</v>
+      </c>
+      <c r="I16" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J16" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="K16" s="87">
+        <v>2</v>
+      </c>
+      <c r="L16" s="88">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="M16" s="89">
+        <v>50</v>
+      </c>
+      <c r="N16" s="90" t="s">
+        <v>61</v>
+      </c>
+      <c r="O16" s="91">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="P16" s="101">
+        <f t="shared" si="2"/>
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="Q16" s="92"/>
+      <c r="R16" s="87"/>
+    </row>
+    <row r="17" spans="1:18" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="67">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="70" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="70" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="74" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" s="70" t="s">
+        <v>85</v>
+      </c>
+      <c r="I17" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="J17" s="74" t="s">
+        <v>48</v>
+      </c>
+      <c r="K17" s="48">
+        <v>2</v>
+      </c>
+      <c r="L17" s="31">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="M17" s="60">
+        <v>50</v>
+      </c>
+      <c r="N17" s="102" t="s">
+        <v>61</v>
+      </c>
+      <c r="O17" s="65">
+        <v>1.9E-2</v>
+      </c>
+      <c r="P17" s="99">
+        <f t="shared" si="2"/>
+        <v>0.95</v>
+      </c>
+      <c r="Q17" s="53"/>
+      <c r="R17" s="48"/>
+    </row>
+    <row r="18" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="67">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="71" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="83" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="H18" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="I18" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="J18" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="K18" s="87">
+        <v>1</v>
+      </c>
+      <c r="L18" s="88">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="C14" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="79" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="56" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" s="67" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" s="56" t="s">
-        <v>51</v>
-      </c>
-      <c r="I14" s="67" t="s">
-        <v>66</v>
-      </c>
-      <c r="J14" s="56" t="s">
-        <v>51</v>
-      </c>
-      <c r="K14" s="50">
-        <v>19</v>
-      </c>
-      <c r="L14" s="30">
-        <f t="shared" si="0"/>
-        <v>95</v>
-      </c>
-      <c r="M14" s="46" t="s">
-        <v>51</v>
-      </c>
-      <c r="N14" s="56" t="s">
-        <v>66</v>
-      </c>
-      <c r="O14" s="67" t="s">
-        <v>51</v>
-      </c>
-      <c r="P14" s="56" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q14" s="56" t="s">
-        <v>66</v>
-      </c>
-      <c r="R14" s="51" t="s">
-        <v>51</v>
-      </c>
+      <c r="M18" s="89">
+        <v>6</v>
+      </c>
+      <c r="N18" s="90" t="s">
+        <v>61</v>
+      </c>
+      <c r="O18" s="91">
+        <v>0.44180000000000003</v>
+      </c>
+      <c r="P18" s="101">
+        <f t="shared" si="2"/>
+        <v>2.6508000000000003</v>
+      </c>
+      <c r="Q18" s="92"/>
+      <c r="R18" s="87"/>
     </row>
-    <row r="15" spans="1:18" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="74">
-        <f>ROW(B15) - ROW($B$9)</f>
-        <v>6</v>
-      </c>
-      <c r="C15" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="78" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="78" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="82" t="s">
-        <v>66</v>
-      </c>
-      <c r="H15" s="78" t="s">
-        <v>43</v>
-      </c>
-      <c r="I15" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="J15" s="78" t="s">
-        <v>49</v>
-      </c>
-      <c r="K15" s="49">
-        <v>2</v>
-      </c>
-      <c r="L15" s="31">
+    <row r="19" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+      <c r="B19" s="67">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="M15" s="61">
-        <v>50</v>
-      </c>
-      <c r="N15" s="70" t="s">
-        <v>64</v>
-      </c>
-      <c r="O15" s="65">
-        <v>1.2699999999999999E-2</v>
-      </c>
-      <c r="P15" s="71">
+      <c r="C19" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="72" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="84" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="75" t="s">
+        <v>63</v>
+      </c>
+      <c r="H19" s="72" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="J19" s="75" t="s">
+        <v>48</v>
+      </c>
+      <c r="K19" s="51">
+        <v>2</v>
+      </c>
+      <c r="L19" s="41">
         <f t="shared" si="1"/>
-        <v>0.63500000000000001</v>
-      </c>
-      <c r="Q15" s="54"/>
-      <c r="R15" s="49"/>
+        <v>10</v>
+      </c>
+      <c r="M19" s="62">
+        <v>11</v>
+      </c>
+      <c r="N19" s="78" t="s">
+        <v>61</v>
+      </c>
+      <c r="O19" s="66">
+        <v>0.1229</v>
+      </c>
+      <c r="P19" s="103">
+        <f t="shared" si="2"/>
+        <v>1.3518999999999999</v>
+      </c>
+      <c r="Q19" s="56"/>
+      <c r="R19" s="51"/>
     </row>
-    <row r="16" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="74">
-        <f>ROW(B16) - ROW($B$9)</f>
-        <v>7</v>
-      </c>
-      <c r="C16" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="79" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="79" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" s="67" t="s">
-        <v>66</v>
-      </c>
-      <c r="H16" s="79" t="s">
-        <v>44</v>
-      </c>
-      <c r="I16" s="35" t="s">
+    <row r="20" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="44"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="121"/>
+      <c r="G20" s="121"/>
+      <c r="H20" s="121"/>
+      <c r="I20" s="121"/>
+      <c r="J20" s="121"/>
+      <c r="K20" s="121"/>
+      <c r="L20" s="122"/>
+      <c r="M20" s="119" t="s">
         <v>69</v>
       </c>
-      <c r="J16" s="56" t="s">
-        <v>51</v>
-      </c>
-      <c r="K16" s="50">
-        <v>1</v>
-      </c>
-      <c r="L16" s="30">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="M16" s="62">
+      <c r="N20" s="120"/>
+      <c r="O20" s="120"/>
+      <c r="P20" s="76">
+        <f>SUM(P10:P19)</f>
+        <v>8.4373000000000005</v>
+      </c>
+      <c r="Q20" s="121"/>
+      <c r="R20" s="122"/>
+    </row>
+    <row r="21" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="N16" s="88" t="s">
-        <v>64</v>
-      </c>
-      <c r="O16" s="66">
-        <v>0.44180000000000003</v>
-      </c>
-      <c r="P16" s="59">
-        <f t="shared" si="1"/>
-        <v>2.6508000000000003</v>
-      </c>
-      <c r="Q16" s="55"/>
-      <c r="R16" s="50"/>
-    </row>
-    <row r="17" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="75">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="C17" s="76" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="80" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="76" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="G17" s="83" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" s="80" t="s">
-        <v>45</v>
-      </c>
-      <c r="I17" s="76" t="s">
+      <c r="D21" s="9"/>
+      <c r="E21" s="123"/>
+      <c r="F21" s="123"/>
+      <c r="G21" s="123"/>
+      <c r="H21" s="123"/>
+      <c r="I21" s="123"/>
+      <c r="J21" s="123"/>
+      <c r="K21" s="123"/>
+      <c r="L21" s="124"/>
+      <c r="M21" s="119" t="s">
         <v>70</v>
       </c>
-      <c r="J17" s="85" t="s">
-        <v>51</v>
-      </c>
-      <c r="K17" s="52">
-        <v>2</v>
-      </c>
-      <c r="L17" s="41">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="M17" s="63">
-        <v>6</v>
-      </c>
-      <c r="N17" s="89" t="s">
-        <v>64</v>
-      </c>
-      <c r="O17" s="68">
-        <v>0.15240000000000001</v>
-      </c>
-      <c r="P17" s="72">
-        <f t="shared" si="1"/>
-        <v>0.9144000000000001</v>
-      </c>
-      <c r="Q17" s="57"/>
-      <c r="R17" s="52"/>
-    </row>
-    <row r="18" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="44"/>
-      <c r="E18" s="96"/>
-      <c r="F18" s="96"/>
-      <c r="G18" s="96"/>
-      <c r="H18" s="96"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="96"/>
-      <c r="K18" s="96"/>
-      <c r="L18" s="97"/>
-      <c r="M18" s="94" t="s">
-        <v>73</v>
-      </c>
-      <c r="N18" s="95"/>
-      <c r="O18" s="95"/>
-      <c r="P18" s="86">
-        <f>SUM(P10:P17)</f>
-        <v>9.3864000000000001</v>
-      </c>
-      <c r="Q18" s="96"/>
-      <c r="R18" s="97"/>
-    </row>
-    <row r="19" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
-      <c r="H19" s="98"/>
-      <c r="I19" s="98"/>
-      <c r="J19" s="98"/>
-      <c r="K19" s="98"/>
-      <c r="L19" s="99"/>
-      <c r="M19" s="94" t="s">
-        <v>74</v>
-      </c>
-      <c r="N19" s="95"/>
-      <c r="O19" s="95"/>
-      <c r="P19" s="87">
-        <f>P18/5</f>
-        <v>1.8772800000000001</v>
-      </c>
-      <c r="Q19" s="98"/>
-      <c r="R19" s="99"/>
+      <c r="N21" s="120"/>
+      <c r="O21" s="120"/>
+      <c r="P21" s="77">
+        <f>P20/5</f>
+        <v>1.6874600000000002</v>
+      </c>
+      <c r="Q21" s="123"/>
+      <c r="R21" s="124"/>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="R3:R8"/>
     <mergeCell ref="J2:R2"/>
-    <mergeCell ref="M18:O18"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="E18:L19"/>
-    <mergeCell ref="Q18:R19"/>
+    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="E20:L21"/>
+    <mergeCell ref="Q20:R21"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="N10" r:id="rId1" xr:uid="{100462C4-FA8F-4D16-8168-575F3EAD1350}"/>
     <hyperlink ref="N11" r:id="rId2" xr:uid="{CC1A75C7-134E-4E20-A6A5-5C056D4918B2}"/>
     <hyperlink ref="N13" r:id="rId3" xr:uid="{FFF28CE1-87AC-4ADE-A95E-16C393CFA042}"/>
-    <hyperlink ref="N12" r:id="rId4" xr:uid="{8C9B39EB-942A-43DB-BCEF-D599850185D7}"/>
-    <hyperlink ref="N16" r:id="rId5" xr:uid="{BB22E13A-9E79-4097-AC4F-F19B2F2754A8}"/>
-    <hyperlink ref="N17" r:id="rId6" xr:uid="{DF4029E5-E8D3-4584-B881-A0621DBEE882}"/>
-    <hyperlink ref="N15" r:id="rId7" xr:uid="{28F214EC-7847-4913-BF43-3F44A00C2675}"/>
+    <hyperlink ref="N18" r:id="rId4" xr:uid="{BB22E13A-9E79-4097-AC4F-F19B2F2754A8}"/>
+    <hyperlink ref="N19" r:id="rId5" xr:uid="{DF4029E5-E8D3-4584-B881-A0621DBEE882}"/>
+    <hyperlink ref="N16" r:id="rId6" xr:uid="{28F214EC-7847-4913-BF43-3F44A00C2675}"/>
+    <hyperlink ref="N12" r:id="rId7" xr:uid="{EF2D9422-FA3A-455D-9387-61549C679B7C}"/>
+    <hyperlink ref="N15" r:id="rId8" xr:uid="{69A342B8-9C85-4B7D-8311-112DBA009E48}"/>
+    <hyperlink ref="N17" r:id="rId9" xr:uid="{FF8D0A6F-0199-49C1-809C-095969B7F3F7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
-  <drawing r:id="rId9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
+  <drawing r:id="rId11"/>
 </worksheet>
 </file>